--- a/docs/samples/평가위원-명단-예시.xlsx
+++ b/docs/samples/평가위원-명단-예시.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
     <col min="2" max="2" width="9.83203125" customWidth="1"/>
@@ -405,7 +405,8 @@
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="5" max="5" width="12.83203125" customWidth="1"/>
     <col min="6" max="6" width="24.83203125" customWidth="1"/>
-    <col min="7" max="7" width="8.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -428,6 +429,9 @@
         <v>이메일</v>
       </c>
       <c r="G1" t="str">
+        <v>연락처</v>
+      </c>
+      <c r="H1" t="str">
         <v>비고</v>
       </c>
     </row>
@@ -451,6 +455,9 @@
         <v>kim.js@example.ac.kr</v>
       </c>
       <c r="G2" t="str">
+        <v>010-1234-5678</v>
+      </c>
+      <c r="H2" t="str">
         <v>위원장</v>
       </c>
     </row>
@@ -474,6 +481,9 @@
         <v>lee.yh@example.re.kr</v>
       </c>
       <c r="G3" t="str">
+        <v>010-2345-6789</v>
+      </c>
+      <c r="H3" t="str">
         <v/>
       </c>
     </row>
@@ -497,6 +507,9 @@
         <v>park@example.law.kr</v>
       </c>
       <c r="G4" t="str">
+        <v>010-3456-7890</v>
+      </c>
+      <c r="H4" t="str">
         <v/>
       </c>
     </row>
@@ -520,6 +533,9 @@
         <v>choi@example.cpa.kr</v>
       </c>
       <c r="G5" t="str">
+        <v>010-4567-8901</v>
+      </c>
+      <c r="H5" t="str">
         <v/>
       </c>
     </row>
@@ -543,6 +559,9 @@
         <v>jung@example.ac.kr</v>
       </c>
       <c r="G6" t="str">
+        <v>010-5678-9012</v>
+      </c>
+      <c r="H6" t="str">
         <v/>
       </c>
     </row>
@@ -566,12 +585,15 @@
         <v>han@example.or.kr</v>
       </c>
       <c r="G7" t="str">
+        <v>010-6789-0123</v>
+      </c>
+      <c r="H7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
   </ignoredErrors>
 </worksheet>
 </file>